--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC753C1-2DA3-4CB5-A872-FA19813BE635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8422E25-C811-4801-91DF-BD818333A64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22500" yWindow="1590" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Fecha</t>
   </si>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E53" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:E53" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E54" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E54" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -568,7 +568,8 @@
         <v>5</v>
       </c>
       <c r="E2" s="1">
-        <v>16.079999999999998</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -585,6 +586,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.559999999999999</v>
       </c>
     </row>
@@ -602,6 +604,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.32</v>
       </c>
     </row>
@@ -616,6 +619,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -633,7 +637,8 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>17.28</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.279999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -650,7 +655,8 @@
         <v>5</v>
       </c>
       <c r="E7" s="1">
-        <v>16.2</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -667,6 +673,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>17.16</v>
       </c>
     </row>
@@ -684,7 +691,8 @@
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>14.4</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.399999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -698,6 +706,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -715,7 +724,8 @@
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>16.920000000000002</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.919999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -732,6 +742,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.32</v>
       </c>
     </row>
@@ -746,6 +757,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -763,6 +775,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.96</v>
       </c>
     </row>
@@ -780,7 +793,8 @@
         <v>5</v>
       </c>
       <c r="E15" s="1">
-        <v>16.079999999999998</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -797,6 +811,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.440000000000001</v>
       </c>
     </row>
@@ -814,6 +829,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.96</v>
       </c>
     </row>
@@ -831,7 +847,8 @@
         <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>16.2</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -845,6 +862,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -862,7 +880,8 @@
         <v>5</v>
       </c>
       <c r="E20" s="1">
-        <v>13.8</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>13.799999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -879,6 +898,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.72</v>
       </c>
     </row>
@@ -896,7 +916,8 @@
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>16.2</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -913,6 +934,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>18</v>
       </c>
     </row>
@@ -930,7 +952,8 @@
         <v>5</v>
       </c>
       <c r="E24" s="1">
-        <v>10.32</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>10.319999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -947,7 +970,8 @@
         <v>5</v>
       </c>
       <c r="E25" s="1">
-        <v>16.8</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.799999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -964,6 +988,7 @@
         <v>5</v>
       </c>
       <c r="E26" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.96</v>
       </c>
     </row>
@@ -978,6 +1003,7 @@
         <v>5</v>
       </c>
       <c r="E27" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -995,6 +1021,7 @@
         <v>5</v>
       </c>
       <c r="E28" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>14.28</v>
       </c>
     </row>
@@ -1009,6 +1036,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -1026,6 +1054,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.559999999999999</v>
       </c>
     </row>
@@ -1043,7 +1072,8 @@
         <v>5</v>
       </c>
       <c r="E31" s="1">
-        <v>17.28</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.279999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1060,7 +1090,8 @@
         <v>5</v>
       </c>
       <c r="E32" s="1">
-        <v>16.079999999999998</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1077,6 +1108,7 @@
         <v>5</v>
       </c>
       <c r="E33" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>18.12</v>
       </c>
     </row>
@@ -1094,7 +1126,8 @@
         <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>16.2</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1111,6 +1144,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>18.48</v>
       </c>
     </row>
@@ -1128,6 +1162,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15</v>
       </c>
     </row>
@@ -1142,6 +1177,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -1159,7 +1195,8 @@
         <v>5</v>
       </c>
       <c r="E38" s="1">
-        <v>16.920000000000002</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.919999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1176,7 +1213,8 @@
         <v>5</v>
       </c>
       <c r="E39" s="1">
-        <v>19.079999999999998</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>19.080000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1190,6 +1228,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -1207,7 +1246,8 @@
         <v>5</v>
       </c>
       <c r="E41" s="1">
-        <v>16.2</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,7 +1264,8 @@
         <v>5</v>
       </c>
       <c r="E42" s="1">
-        <v>16.079999999999998</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1241,7 +1282,8 @@
         <v>5</v>
       </c>
       <c r="E43" s="1">
-        <v>17.760000000000002</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.759999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1258,7 +1300,8 @@
         <v>5</v>
       </c>
       <c r="E44" s="1">
-        <v>15.6</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.600000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1275,7 +1318,8 @@
         <v>5</v>
       </c>
       <c r="E45" s="1">
-        <v>14.88</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.879999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1289,6 +1333,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>0</v>
       </c>
     </row>
@@ -1306,6 +1351,7 @@
         <v>5</v>
       </c>
       <c r="E47" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.96</v>
       </c>
     </row>
@@ -1323,6 +1369,7 @@
         <v>5</v>
       </c>
       <c r="E48" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.68</v>
       </c>
     </row>
@@ -1340,6 +1387,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>17.04</v>
       </c>
     </row>
@@ -1357,6 +1405,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>18</v>
       </c>
     </row>
@@ -1374,7 +1423,8 @@
         <v>5</v>
       </c>
       <c r="E51" s="1">
-        <v>14.88</v>
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.879999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1391,6 +1441,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>17.64</v>
       </c>
     </row>
@@ -1408,7 +1459,26 @@
         <v>5</v>
       </c>
       <c r="E53" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46602</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54">
+        <v>1.29</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8422E25-C811-4801-91DF-BD818333A64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B47" t="s">
         <v>22</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>25</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B53" t="s">
         <v>31</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46602</v>
+        <v>46612</v>
       </c>
       <c r="B54" t="s">
         <v>28</v>

--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F01B7E-F20A-4BDD-93FE-2BD74216CE4E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
   <si>
     <t>Fecha</t>
   </si>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t>Petko_Avramov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca _Valentino_Scaffetti </t>
   </si>
   <si>
     <t>Jorge_vicaria</t>
@@ -220,8 +217,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E54" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:E54" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E76" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E76" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -530,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -556,10 +553,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>1.34</v>
@@ -574,7 +571,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -592,7 +589,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -610,7 +607,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -625,7 +622,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -643,7 +640,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -661,7 +658,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -679,7 +676,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -697,7 +694,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -712,7 +709,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -730,7 +727,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -748,7 +745,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -763,7 +760,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -781,7 +778,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -799,7 +796,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -817,7 +814,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -835,7 +832,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -853,7 +850,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
@@ -868,7 +865,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -886,7 +883,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -904,7 +901,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -922,7 +919,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
@@ -940,7 +937,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>26</v>
@@ -958,527 +955,904 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.799999999999997</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>1.33</v>
+        <v>27</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>15.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>1.19</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28">
-        <v>1.19</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>14.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>1.38</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.559999999999999</v>
+        <v>17.279999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.279999999999998</v>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.080000000000002</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>18.12</v>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.200000000000003</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>18.48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36">
-        <v>1.25</v>
+        <v>12</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>1.41</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>16.919999999999998</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.919999999999998</v>
+        <v>19.080000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39">
-        <v>1.59</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
       <c r="E39" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>19.080000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C40">
+        <v>1.35</v>
       </c>
       <c r="D40">
         <v>5</v>
       </c>
       <c r="E40" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.200000000000003</v>
+        <v>16.080000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C42">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
       <c r="E42" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.080000000000002</v>
+        <v>17.759999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
       <c r="E43" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.759999999999998</v>
+        <v>15.600000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C44">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
       <c r="E44" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>15.600000000000001</v>
+        <v>14.879999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="D45">
         <v>5</v>
       </c>
       <c r="E45" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>14.879999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="C46">
+        <v>1.33</v>
       </c>
       <c r="D46">
         <v>5</v>
       </c>
       <c r="E46" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C47">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="D47">
         <v>5</v>
       </c>
       <c r="E47" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>15.96</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="D48">
         <v>5</v>
       </c>
       <c r="E48" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.68</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46612</v>
-      </c>
-      <c r="B49" t="s">
-        <v>24</v>
+        <v>46247</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C49">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="D49">
         <v>5</v>
       </c>
       <c r="E49" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.04</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46612</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>25</v>
+        <v>46247</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
       </c>
       <c r="C50">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="D50">
         <v>5</v>
       </c>
       <c r="E50" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>18</v>
+        <v>14.879999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C51">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="D51">
         <v>5</v>
       </c>
       <c r="E51" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>14.879999999999999</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46612</v>
+        <v>46247</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
       </c>
       <c r="C52">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="D52">
         <v>5</v>
       </c>
       <c r="E52" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.64</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46612</v>
+        <v>46259</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53">
-        <v>1.45</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>5</v>
-      </c>
-      <c r="E53" s="1">
-        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46612</v>
+        <v>46259</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C54">
+        <v>1.44</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.279999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55">
         <v>1.29</v>
       </c>
-      <c r="D54">
-        <v>5</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>15.48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57">
+        <v>1.38</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.559999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58">
+        <v>1.61</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <v>1.31</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60">
+        <v>1.39</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61">
+        <v>1.17</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>1.35</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.200000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65">
+        <v>1.2</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.399999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66">
+        <v>1.48</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.759999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67">
+        <v>1.31</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68">
+        <v>1.24</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>14.879999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69">
+        <v>1.4</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.799999999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70">
+        <v>1.42</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71">
+        <v>1.28</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73">
+        <v>1.46</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>17.52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74">
+        <v>1.33</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>15.96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75">
+        <v>1.5</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+      <c r="E75" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76">
+        <v>1.4</v>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.799999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F01B7E-F20A-4BDD-93FE-2BD74216CE4E}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C0AED4-A525-474B-8231-27D5BEC5DAC2}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Fecha</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
+  </si>
+  <si>
+    <t>Presley_Osarenkhoe</t>
   </si>
 </sst>
 </file>
@@ -217,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E76" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:E76" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E77" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E77" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -527,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1855,6 +1858,24 @@
         <v>16.799999999999997</v>
       </c>
     </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77">
+        <v>1.41</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77" s="1">
+        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
+        <v>16.919999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C0AED4-A525-474B-8231-27D5BEC5DAC2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956A9962-FF55-421C-A3A5-C4892B465CD4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Fecha</t>
   </si>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E77" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:E77" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:E76" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E76" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1604,12 +1604,15 @@
       <c r="B62" t="s">
         <v>14</v>
       </c>
+      <c r="C62">
+        <v>1.56</v>
+      </c>
       <c r="D62">
         <v>5</v>
       </c>
       <c r="E62" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1775,33 +1778,36 @@
       <c r="A72" s="2">
         <v>46259</v>
       </c>
-      <c r="B72" t="s">
-        <v>24</v>
+      <c r="B72" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72">
+        <v>1.46</v>
       </c>
       <c r="D72">
         <v>5</v>
       </c>
       <c r="E72" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>46259</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>25</v>
+      <c r="B73" t="s">
+        <v>26</v>
       </c>
       <c r="C73">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="D73">
         <v>5</v>
       </c>
       <c r="E73" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>17.52</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1809,17 +1815,17 @@
         <v>46259</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C74">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="D74">
         <v>5</v>
       </c>
       <c r="E74" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>15.96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1827,51 +1833,33 @@
         <v>46259</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C75">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D75">
         <v>5</v>
       </c>
       <c r="E75" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>18</v>
+        <v>16.799999999999997</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>46259</v>
       </c>
-      <c r="B76" t="s">
-        <v>27</v>
+      <c r="B76" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C76">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="D76">
         <v>5</v>
       </c>
       <c r="E76" s="1">
-        <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>16.799999999999997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <v>46259</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C77">
-        <v>1.41</v>
-      </c>
-      <c r="D77">
-        <v>5</v>
-      </c>
-      <c r="E77" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
         <v>16.919999999999998</v>
       </c>

--- a/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AEROBICO_5MIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956A9962-FF55-421C-A3A5-C4892B465CD4}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{70C7CA30-4A11-43CA-A210-8E38ACFDF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A30F84B-0D3B-43C3-BC3B-59CE6A14E4BB}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -1499,12 +1499,15 @@
       <c r="B56" t="s">
         <v>8</v>
       </c>
+      <c r="C56">
+        <v>1.26</v>
+      </c>
       <c r="D56">
         <v>5</v>
       </c>
       <c r="E56" s="1">
         <f>(Tabla1[[#This Row],[Distancia]]/Tabla1[[#This Row],[Tiempo ]])*60</f>
-        <v>0</v>
+        <v>15.120000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
